--- a/mappingCorps/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
+++ b/mappingCorps/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:18:14+00:00</t>
+    <t>2026-08-05T09:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -573,7 +573,7 @@
 https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-observation</t>
   </si>
   <si>
-    <t>Observations associées et rattachées à cette entree</t>
+    <t>Observations associées</t>
   </si>
 </sst>
 </file>
